--- a/.xlsx files/Oil_Gas Statistics.xlsx
+++ b/.xlsx files/Oil_Gas Statistics.xlsx
@@ -329,7 +329,7 @@
     <t>Isnti</t>
   </si>
   <si>
-    <t>lasri</t>
+    <t>Lasri</t>
   </si>
   <si>
     <t>Lydroa</t>
